--- a/data/trans_orig/IP16A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>23844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31998</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20587</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>31871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34061</t>
+          <t>34628</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44018</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>50907</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>89310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113508</t>
+          <t>114590</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75467</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>75118</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>93012</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>155716</t>
+          <t>154634</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>181641</t>
+          <t>179914</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39582</t>
+          <t>38856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>26535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27396</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20173</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>27555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36031</t>
+          <t>35147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67876</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89891</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64620</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>86300</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>138008</t>
+          <t>138640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>171072</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97746</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128090</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>209275</t>
+          <t>207506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>241707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18732</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31709</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24025</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>26713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>33174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14291</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>63,81%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28829</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>31104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53571</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63534</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132584</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>89534</t>
+          <t>89902</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>110230</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>83851</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>102550</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>178061</t>
+          <t>178693</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>206485</t>
+          <t>207254</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>32004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45585</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46588</t>
+          <t>47154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>34663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>26651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74608</t>
+          <t>75190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>53823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36609</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91760</t>
+          <t>84566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33326</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17177</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28643</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>45561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>89860</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>91778</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>172684</t>
+          <t>171925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>134490</t>
+          <t>133859</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>115070</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>187232</t>
+          <t>187991</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>246380</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
